--- a/05_Manuscript/results/5_factor_reduced.xlsx
+++ b/05_Manuscript/results/5_factor_reduced.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erinbuchanan/GitHub/Research/2_projects/00_not_used_while/Gen-Scale/05_Manuscript/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F3567F-79C4-D841-B656-D68D3D4BAB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9ED626B-5996-AA41-B77A-7CB757E25910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -252,17 +252,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
